--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G115" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P117" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22664,7 +22664,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G117" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22664,7 +22664,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G117" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,17 +10450,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P117" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,17 +9859,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.74</v>
+        <v>4.32</v>
       </c>
       <c r="R51" t="n">
-        <v>3.94</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P117" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,17 +9662,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.23</v>
+        <v>3.74</v>
       </c>
       <c r="R48" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>8.210000000000001</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="R53" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.74</v>
+        <v>4.32</v>
       </c>
       <c r="R58" t="n">
-        <v>3.94</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G117" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,17 +9662,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,17 +9859,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="R52" t="n">
-        <v>3.65</v>
+        <v>3.01</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.06</v>
+        <v>4.32</v>
       </c>
       <c r="R55" t="n">
-        <v>3.13</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R56" t="n">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>8.210000000000001</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G117" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI118"/>
+  <dimension ref="A1:BI117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="R47" t="n">
-        <v>3.65</v>
+        <v>3.01</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.57</v>
+        <v>3.74</v>
       </c>
       <c r="R49" t="n">
-        <v>4.9</v>
+        <v>3.94</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.96</v>
+        <v>1.32</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.23</v>
+        <v>4.32</v>
       </c>
       <c r="R50" t="n">
-        <v>3.58</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.06</v>
+        <v>3.23</v>
       </c>
       <c r="R51" t="n">
-        <v>3.13</v>
+        <v>3.58</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R52" t="n">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.32</v>
+        <v>1.98</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.32</v>
+        <v>3.11</v>
       </c>
       <c r="R55" t="n">
-        <v>8.210000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.74</v>
+        <v>3.06</v>
       </c>
       <c r="R57" t="n">
-        <v>3.94</v>
+        <v>3.13</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23403,27 +23403,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23591,203 +23591,6 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46122.875</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>North Texas</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Sporting KC II</t>
-        </is>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N118" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI118" s="3" t="n">
         <v>46122.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,17 +9662,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.74</v>
+        <v>2.94</v>
       </c>
       <c r="R49" t="n">
-        <v>3.94</v>
+        <v>2.45</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.32</v>
+        <v>3.74</v>
       </c>
       <c r="R50" t="n">
-        <v>8.210000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.85</v>
+        <v>1.96</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="R52" t="n">
-        <v>2.45</v>
+        <v>3.58</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,17 +10844,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.57</v>
+        <v>4.32</v>
       </c>
       <c r="R54" t="n">
-        <v>4.9</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q57" t="n">
         <v>3.06</v>
       </c>
       <c r="R57" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.19</v>
+        <v>3.18</v>
       </c>
       <c r="Q62" t="n">
-        <v>7.7</v>
+        <v>3.3</v>
       </c>
       <c r="R62" t="n">
-        <v>14.1</v>
+        <v>2.15</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P116" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="R49" t="n">
-        <v>2.45</v>
+        <v>3.01</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="R52" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.98</v>
+        <v>1.32</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.11</v>
+        <v>4.32</v>
       </c>
       <c r="R53" t="n">
-        <v>3.65</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.32</v>
+        <v>3.74</v>
       </c>
       <c r="R54" t="n">
-        <v>8.210000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.06</v>
+        <v>3.23</v>
       </c>
       <c r="R56" t="n">
-        <v>3.13</v>
+        <v>3.58</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q57" t="n">
         <v>3.06</v>
       </c>
       <c r="R57" t="n">
-        <v>3.01</v>
+        <v>3.13</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.9</v>
+        <v>3.12</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R61" t="n">
-        <v>3.72</v>
+        <v>2.15</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.18</v>
+        <v>2.47</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R62" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.19</v>
+        <v>1.9</v>
       </c>
       <c r="Q69" t="n">
-        <v>7.7</v>
+        <v>3.5</v>
       </c>
       <c r="R69" t="n">
-        <v>14.1</v>
+        <v>3.72</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P116" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.98</v>
+        <v>1.32</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.11</v>
+        <v>4.32</v>
       </c>
       <c r="R52" t="n">
-        <v>3.65</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.32</v>
+        <v>2.85</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.32</v>
+        <v>2.94</v>
       </c>
       <c r="R53" t="n">
-        <v>8.210000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.74</v>
+        <v>3.11</v>
       </c>
       <c r="R54" t="n">
-        <v>3.94</v>
+        <v>3.65</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,17 +11238,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.06</v>
+        <v>3.57</v>
       </c>
       <c r="R57" t="n">
-        <v>3.13</v>
+        <v>4.9</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.57</v>
+        <v>3.23</v>
       </c>
       <c r="R58" t="n">
-        <v>4.9</v>
+        <v>3.58</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="R69" t="n">
-        <v>3.72</v>
+        <v>4.55</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.18</v>
+        <v>2.47</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R70" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.19</v>
+        <v>3.86</v>
       </c>
       <c r="Q72" t="n">
-        <v>7.7</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>14.1</v>
+        <v>1.96</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14784,17 +14784,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.97</v>
+        <v>2.48</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="R95" t="n">
-        <v>3.99</v>
+        <v>2.7</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G116" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.32</v>
+        <v>3.74</v>
       </c>
       <c r="R52" t="n">
-        <v>8.210000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.85</v>
+        <v>1.32</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.94</v>
+        <v>4.32</v>
       </c>
       <c r="R53" t="n">
-        <v>2.45</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="R54" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="R55" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.23</v>
+        <v>3.06</v>
       </c>
       <c r="R58" t="n">
-        <v>3.58</v>
+        <v>3.13</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.18</v>
+        <v>2.47</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R65" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.5</v>
+        <v>3.86</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R71" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.86</v>
+        <v>1.71</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.3</v>
+        <v>3.82</v>
       </c>
       <c r="R72" t="n">
-        <v>1.96</v>
+        <v>4.55</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="Q94" t="n">
-        <v>5.27</v>
+        <v>3.82</v>
       </c>
       <c r="R94" t="n">
-        <v>9.300000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22664,7 +22664,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G116" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.06</v>
+        <v>3.23</v>
       </c>
       <c r="R48" t="n">
-        <v>3.01</v>
+        <v>3.58</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.32</v>
+        <v>3.57</v>
       </c>
       <c r="R53" t="n">
-        <v>8.210000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.85</v>
+        <v>1.32</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.94</v>
+        <v>4.32</v>
       </c>
       <c r="R54" t="n">
-        <v>2.45</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="R55" t="n">
-        <v>3.65</v>
+        <v>3.13</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.57</v>
+        <v>3.11</v>
       </c>
       <c r="R57" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R58" t="n">
-        <v>3.13</v>
+        <v>2.45</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R60" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.19</v>
+        <v>1.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>7.7</v>
+        <v>3.5</v>
       </c>
       <c r="R62" t="n">
-        <v>14.1</v>
+        <v>3.72</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.9</v>
+        <v>1.19</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>7.7</v>
       </c>
       <c r="R63" t="n">
-        <v>3.72</v>
+        <v>14.1</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.71</v>
+        <v>3.86</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>4.55</v>
+        <v>1.96</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.94</v>
+        <v>3.55</v>
       </c>
       <c r="R76" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="R80" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22664,7 +22664,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G116" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,55 +9863,55 @@
         </is>
       </c>
       <c r="P48" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="R48" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q48" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="R48" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,17 +10056,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.61</v>
+        <v>2.28</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.57</v>
+        <v>3.06</v>
       </c>
       <c r="R53" t="n">
-        <v>4.9</v>
+        <v>3.01</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.32</v>
+        <v>3.74</v>
       </c>
       <c r="R54" t="n">
-        <v>8.210000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.06</v>
+        <v>3.23</v>
       </c>
       <c r="R55" t="n">
-        <v>3.13</v>
+        <v>3.58</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="R57" t="n">
-        <v>3.65</v>
+        <v>3.13</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R60" t="n">
         <v>2.15</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.19</v>
+        <v>3.18</v>
       </c>
       <c r="Q63" t="n">
-        <v>7.7</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>14.1</v>
+        <v>2.15</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.47</v>
+        <v>1.19</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.15</v>
+        <v>7.7</v>
       </c>
       <c r="R70" t="n">
-        <v>2.8</v>
+        <v>14.1</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.86</v>
+        <v>2.47</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R72" t="n">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R76" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.94</v>
+        <v>3.55</v>
       </c>
       <c r="R77" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="R88" t="n">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G116" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.32</v>
+        <v>3.23</v>
       </c>
       <c r="R47" t="n">
-        <v>8.210000000000001</v>
+        <v>3.58</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.61</v>
+        <v>2.28</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.57</v>
+        <v>3.06</v>
       </c>
       <c r="R48" t="n">
-        <v>4.9</v>
+        <v>3.01</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,17 +10056,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q53" t="n">
         <v>3.06</v>
       </c>
       <c r="R53" t="n">
-        <v>3.01</v>
+        <v>3.13</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R57" t="n">
-        <v>3.13</v>
+        <v>2.45</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R60" t="n">
         <v>2.15</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.71</v>
+        <v>1.19</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.82</v>
+        <v>7.7</v>
       </c>
       <c r="R64" t="n">
-        <v>4.55</v>
+        <v>14.1</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.19</v>
+        <v>3.12</v>
       </c>
       <c r="Q70" t="n">
-        <v>7.7</v>
+        <v>3.45</v>
       </c>
       <c r="R70" t="n">
-        <v>14.1</v>
+        <v>2.15</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R72" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="R77" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.13</v>
+        <v>3.33</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.53</v>
+        <v>3.94</v>
       </c>
       <c r="R80" t="n">
-        <v>3.48</v>
+        <v>2.17</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.94</v>
+        <v>3.55</v>
       </c>
       <c r="R82" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.35</v>
+        <v>3.82</v>
       </c>
       <c r="R88" t="n">
-        <v>2.99</v>
+        <v>4.33</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="Q89" t="n">
-        <v>5.27</v>
+        <v>3.35</v>
       </c>
       <c r="R89" t="n">
-        <v>9.300000000000001</v>
+        <v>2.99</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G116" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,55 +9666,55 @@
         </is>
       </c>
       <c r="P47" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="R47" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q47" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="R47" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R48" t="n">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,17 +10056,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.06</v>
+        <v>3.74</v>
       </c>
       <c r="R53" t="n">
-        <v>3.13</v>
+        <v>3.94</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,17 +11041,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="R57" t="n">
-        <v>2.45</v>
+        <v>3.13</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.32</v>
+        <v>3.23</v>
       </c>
       <c r="R58" t="n">
-        <v>8.210000000000001</v>
+        <v>3.58</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.9</v>
+        <v>3.86</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R62" t="n">
-        <v>3.72</v>
+        <v>1.96</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.47</v>
+        <v>1.9</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R67" t="n">
-        <v>2.8</v>
+        <v>3.72</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="R76" t="n">
-        <v>2.47</v>
+        <v>3.48</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="Q84" t="n">
-        <v>5.27</v>
+        <v>3.35</v>
       </c>
       <c r="R84" t="n">
-        <v>9.300000000000001</v>
+        <v>2.99</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P116" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.57</v>
+        <v>3.23</v>
       </c>
       <c r="R47" t="n">
-        <v>4.9</v>
+        <v>3.58</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.32</v>
+        <v>3.06</v>
       </c>
       <c r="R51" t="n">
-        <v>8.210000000000001</v>
+        <v>3.01</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.74</v>
+        <v>3.57</v>
       </c>
       <c r="R53" t="n">
-        <v>3.94</v>
+        <v>4.9</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R55" t="n">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.06</v>
+        <v>3.74</v>
       </c>
       <c r="R57" t="n">
-        <v>3.13</v>
+        <v>3.94</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.96</v>
+        <v>1.32</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.23</v>
+        <v>4.32</v>
       </c>
       <c r="R58" t="n">
-        <v>3.58</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.86</v>
+        <v>1.71</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.3</v>
+        <v>3.82</v>
       </c>
       <c r="R62" t="n">
-        <v>1.96</v>
+        <v>4.55</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.5</v>
+        <v>3.86</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.19</v>
+        <v>2.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>7.7</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>14.1</v>
+        <v>2.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R79" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="R81" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.81</v>
+        <v>3.03</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.82</v>
+        <v>3.19</v>
       </c>
       <c r="R93" t="n">
-        <v>4.33</v>
+        <v>2.31</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22664,7 +22664,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P116" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI117"/>
+  <dimension ref="A1:BI120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46122.52083333334</v>
+        <v>46122.5</v>
       </c>
     </row>
     <row r="25">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46122.53125</v>
+        <v>46122.5</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46122.54166666666</v>
+        <v>46122.52083333334</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46122.54166666666</v>
+        <v>46122.53125</v>
       </c>
     </row>
     <row r="28">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46122.55555555555</v>
+        <v>46122.54166666666</v>
       </c>
     </row>
     <row r="38">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46122.5625</v>
+        <v>46122.54166666666</v>
       </c>
     </row>
     <row r="39">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46122.5625</v>
+        <v>46122.55555555555</v>
       </c>
     </row>
     <row r="40">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46122.58333333334</v>
+        <v>46122.5625</v>
       </c>
     </row>
     <row r="44">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46122.58333333334</v>
+        <v>46122.5625</v>
       </c>
     </row>
     <row r="45">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46122.58333333334</v>
+        <v>46122.57291666666</v>
       </c>
     </row>
     <row r="46">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46122.60416666666</v>
+        <v>46122.58333333334</v>
       </c>
     </row>
     <row r="48">
@@ -9810,12 +9810,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46122.60416666666</v>
+        <v>46122.58333333334</v>
       </c>
     </row>
     <row r="49">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46122.60416666666</v>
+        <v>46122.58333333334</v>
       </c>
     </row>
     <row r="50">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="R51" t="n">
-        <v>3.01</v>
+        <v>3.65</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R52" t="n">
-        <v>3.13</v>
+        <v>2.45</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.57</v>
+        <v>3.74</v>
       </c>
       <c r="R53" t="n">
-        <v>4.9</v>
+        <v>3.94</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.85</v>
+        <v>1.96</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="R55" t="n">
-        <v>2.45</v>
+        <v>3.58</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.98</v>
+        <v>1.32</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.11</v>
+        <v>4.32</v>
       </c>
       <c r="R56" t="n">
-        <v>3.65</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.74</v>
+        <v>3.57</v>
       </c>
       <c r="R57" t="n">
-        <v>3.94</v>
+        <v>4.9</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>8.210000000000001</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46122.61458333334</v>
+        <v>46122.60416666666</v>
       </c>
     </row>
     <row r="60">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.45</v>
+        <v>3.06</v>
       </c>
       <c r="R60" t="n">
-        <v>2.15</v>
+        <v>3.13</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46122.625</v>
+        <v>46122.60416666666</v>
       </c>
     </row>
     <row r="61">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46122.625</v>
+        <v>46122.60416666666</v>
       </c>
     </row>
     <row r="62">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46122.625</v>
+        <v>46122.61458333334</v>
       </c>
     </row>
     <row r="63">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.19</v>
+        <v>3.86</v>
       </c>
       <c r="Q65" t="n">
-        <v>7.7</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>14.1</v>
+        <v>1.96</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="R70" t="n">
-        <v>3.72</v>
+        <v>4.55</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.18</v>
+        <v>2.47</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R72" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46122.63541666666</v>
+        <v>46122.625</v>
       </c>
     </row>
     <row r="75">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46122.63541666666</v>
+        <v>46122.625</v>
       </c>
     </row>
     <row r="76">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46122.64583333334</v>
+        <v>46122.625</v>
       </c>
     </row>
     <row r="77">
@@ -15523,12 +15523,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46122.64583333334</v>
+        <v>46122.63541666666</v>
       </c>
     </row>
     <row r="78">
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46122.64583333334</v>
+        <v>46122.63541666666</v>
       </c>
     </row>
     <row r="79">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="R81" t="n">
-        <v>3.48</v>
+        <v>2.47</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="R82" t="n">
-        <v>2.47</v>
+        <v>3.48</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16705,12 +16705,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>46122.65625</v>
+        <v>46122.64583333334</v>
       </c>
     </row>
     <row r="84">
@@ -16902,27 +16902,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46122.65625</v>
+        <v>46122.64583333334</v>
       </c>
     </row>
     <row r="85">
@@ -17099,27 +17099,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46122.65625</v>
+        <v>46122.64583333334</v>
       </c>
     </row>
     <row r="86">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.81</v>
+        <v>3.03</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.82</v>
+        <v>3.19</v>
       </c>
       <c r="R91" t="n">
-        <v>4.33</v>
+        <v>2.31</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19069,12 +19069,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46122.66666666666</v>
+        <v>46122.65625</v>
       </c>
     </row>
     <row r="96">
@@ -19266,12 +19266,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46122.66666666666</v>
+        <v>46122.65625</v>
       </c>
     </row>
     <row r="97">
@@ -19463,27 +19463,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46122.66666666666</v>
+        <v>46122.65625</v>
       </c>
     </row>
     <row r="98">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19857,12 +19857,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.29</v>
+        <v>2.48</v>
       </c>
       <c r="Q99" t="n">
-        <v>6.55</v>
+        <v>3.25</v>
       </c>
       <c r="R99" t="n">
-        <v>11.4</v>
+        <v>2.7</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46122.67013888889</v>
+        <v>46122.66666666666</v>
       </c>
     </row>
     <row r="100">
@@ -20054,27 +20054,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="Q100" t="n">
-        <v>4.3</v>
+        <v>3.88</v>
       </c>
       <c r="R100" t="n">
-        <v>4.32</v>
+        <v>3.99</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46122.67708333334</v>
+        <v>46122.66666666666</v>
       </c>
     </row>
     <row r="101">
@@ -20251,27 +20251,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46122.69791666666</v>
+        <v>46122.66666666666</v>
       </c>
     </row>
     <row r="102">
@@ -20448,27 +20448,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.61</v>
+        <v>1.29</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.3</v>
+        <v>6.55</v>
       </c>
       <c r="R102" t="n">
-        <v>1.87</v>
+        <v>11.4</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46122.8125</v>
+        <v>46122.67013888889</v>
       </c>
     </row>
     <row r="103">
@@ -20645,12 +20645,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46122.83333333334</v>
+        <v>46122.67708333334</v>
       </c>
     </row>
     <row r="104">
@@ -20842,27 +20842,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46122.85416666666</v>
+        <v>46122.69791666666</v>
       </c>
     </row>
     <row r="105">
@@ -21039,27 +21039,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46122.875</v>
+        <v>46122.8125</v>
       </c>
     </row>
     <row r="106">
@@ -21236,12 +21236,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21424,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3" t="n">
-        <v>46122.875</v>
+        <v>46122.83333333334</v>
       </c>
     </row>
     <row r="107">
@@ -21433,12 +21433,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21621,7 +21621,7 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3" t="n">
-        <v>46122.875</v>
+        <v>46122.85416666666</v>
       </c>
     </row>
     <row r="108">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22664,7 +22664,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23591,6 +23591,597 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
+        <v>46122.875</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Velež</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Sloga Doboj</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI118" s="3" t="n">
+        <v>46122.875</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Radnik Bijeljina</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Željezničar</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI119" s="3" t="n">
+        <v>46122.875</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>North Texas</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Sporting KC II</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI120" s="3" t="n">
         <v>46122.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R38" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.06</v>
+        <v>4.32</v>
       </c>
       <c r="R54" t="n">
-        <v>3.01</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.96</v>
+        <v>2.85</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="R55" t="n">
-        <v>3.58</v>
+        <v>2.45</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.32</v>
+        <v>3.57</v>
       </c>
       <c r="R56" t="n">
-        <v>8.210000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.61</v>
+        <v>2.28</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.57</v>
+        <v>3.06</v>
       </c>
       <c r="R57" t="n">
-        <v>4.9</v>
+        <v>3.01</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.06</v>
+        <v>3.74</v>
       </c>
       <c r="R60" t="n">
-        <v>3.13</v>
+        <v>3.94</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.25</v>
+        <v>3.82</v>
       </c>
       <c r="R64" t="n">
-        <v>2.65</v>
+        <v>4.55</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.9</v>
+        <v>3.86</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R71" t="n">
-        <v>3.72</v>
+        <v>1.96</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.47</v>
+        <v>1.9</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R72" t="n">
-        <v>2.8</v>
+        <v>3.72</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14784,17 +14784,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R80" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="R81" t="n">
-        <v>2.47</v>
+        <v>3.48</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.23</v>
+        <v>3.06</v>
       </c>
       <c r="R50" t="n">
-        <v>3.58</v>
+        <v>3.01</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.32</v>
+        <v>3.74</v>
       </c>
       <c r="R54" t="n">
-        <v>8.210000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.85</v>
+        <v>1.98</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="R55" t="n">
-        <v>2.45</v>
+        <v>3.65</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.06</v>
+        <v>3.23</v>
       </c>
       <c r="R58" t="n">
-        <v>3.13</v>
+        <v>3.58</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.74</v>
+        <v>2.94</v>
       </c>
       <c r="R60" t="n">
-        <v>3.94</v>
+        <v>2.45</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="R61" t="n">
-        <v>3.65</v>
+        <v>3.13</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.18</v>
+        <v>1.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>2.15</v>
+        <v>3.72</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.71</v>
+        <v>3.18</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>4.55</v>
+        <v>2.15</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.86</v>
+        <v>2.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R71" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="R72" t="n">
-        <v>3.72</v>
+        <v>4.55</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.47</v>
+        <v>3.12</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R80" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R84" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.33</v>
+        <v>2.13</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.94</v>
+        <v>3.53</v>
       </c>
       <c r="R85" t="n">
-        <v>2.17</v>
+        <v>3.48</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="R87" t="n">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="Q89" t="n">
-        <v>5.27</v>
+        <v>3.82</v>
       </c>
       <c r="R89" t="n">
-        <v>9.300000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>3.03</v>
+        <v>1.39</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.19</v>
+        <v>5.27</v>
       </c>
       <c r="R90" t="n">
-        <v>2.31</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.48</v>
+        <v>1.97</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.25</v>
+        <v>3.88</v>
       </c>
       <c r="R101" t="n">
-        <v>2.7</v>
+        <v>3.99</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R37" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.57</v>
+        <v>3.06</v>
       </c>
       <c r="R51" t="n">
-        <v>4.9</v>
+        <v>3.13</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>8.210000000000001</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.11</v>
+        <v>3.57</v>
       </c>
       <c r="R55" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="R58" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.85</v>
+        <v>1.32</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.94</v>
+        <v>4.32</v>
       </c>
       <c r="R60" t="n">
-        <v>2.45</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R61" t="n">
-        <v>3.13</v>
+        <v>2.45</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.9</v>
+        <v>3.18</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>3.72</v>
+        <v>2.15</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.86</v>
+        <v>2.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R66" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.19</v>
+        <v>1.9</v>
       </c>
       <c r="Q67" t="n">
-        <v>7.7</v>
+        <v>3.5</v>
       </c>
       <c r="R67" t="n">
-        <v>14.1</v>
+        <v>3.72</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14981,17 +14981,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="R83" t="n">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.57</v>
+        <v>3.11</v>
       </c>
       <c r="R55" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,17 +11435,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.74</v>
+        <v>3.57</v>
       </c>
       <c r="R57" t="n">
-        <v>3.94</v>
+        <v>4.9</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="R58" t="n">
-        <v>3.65</v>
+        <v>3.13</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>8.210000000000001</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.94</v>
+        <v>3.74</v>
       </c>
       <c r="R61" t="n">
-        <v>2.45</v>
+        <v>3.94</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.18</v>
+        <v>3.86</v>
       </c>
       <c r="Q63" t="n">
         <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.47</v>
+        <v>3.12</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="R65" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.19</v>
+        <v>1.9</v>
       </c>
       <c r="Q70" t="n">
-        <v>7.7</v>
+        <v>3.5</v>
       </c>
       <c r="R70" t="n">
-        <v>14.1</v>
+        <v>3.72</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14981,17 +14981,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>8.18</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="R83" t="n">
-        <v>2.47</v>
+        <v>3.48</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.35</v>
+        <v>3.82</v>
       </c>
       <c r="R94" t="n">
-        <v>2.99</v>
+        <v>4.33</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="R97" t="n">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,17 +10253,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.85</v>
+        <v>1.32</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.94</v>
+        <v>4.32</v>
       </c>
       <c r="R52" t="n">
-        <v>2.45</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R54" t="n">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>8.210000000000001</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.57</v>
+        <v>3.06</v>
       </c>
       <c r="R57" t="n">
-        <v>4.9</v>
+        <v>3.13</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q58" t="n">
         <v>3.06</v>
       </c>
       <c r="R58" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12420,17 +12420,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.86</v>
+        <v>2.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R63" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.18</v>
+        <v>1.71</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>3.82</v>
       </c>
       <c r="R64" t="n">
-        <v>2.15</v>
+        <v>4.55</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.9</v>
+        <v>1.27</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.5</v>
+        <v>5.68</v>
       </c>
       <c r="R70" t="n">
-        <v>3.72</v>
+        <v>8.18</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.71</v>
+        <v>3.18</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="R71" t="n">
-        <v>4.55</v>
+        <v>2.15</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="R73" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.19</v>
+        <v>3.86</v>
       </c>
       <c r="Q74" t="n">
-        <v>7.7</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>14.1</v>
+        <v>1.96</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15375,17 +15375,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>8.18</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="R80" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23649,7 +23649,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R35" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="Q38" t="n">
         <v>3.35</v>
       </c>
       <c r="R38" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.28</v>
+        <v>1.97</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>2.04</v>
+        <v>3.38</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.8</v>
+        <v>2.99</v>
       </c>
       <c r="R43" t="n">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.57</v>
+        <v>3.23</v>
       </c>
       <c r="R50" t="n">
-        <v>4.9</v>
+        <v>3.58</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.32</v>
+        <v>2.85</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.32</v>
+        <v>2.94</v>
       </c>
       <c r="R52" t="n">
-        <v>8.210000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,17 +10844,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.94</v>
+        <v>3.74</v>
       </c>
       <c r="R54" t="n">
-        <v>2.45</v>
+        <v>3.94</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12420,17 +12420,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>2.65</v>
+        <v>3.72</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.71</v>
+        <v>3.18</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>4.55</v>
+        <v>2.15</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>8.18</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R71" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.12</v>
+        <v>1.27</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.45</v>
+        <v>5.68</v>
       </c>
       <c r="R73" t="n">
-        <v>2.15</v>
+        <v>8.18</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14981,17 +14981,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15375,17 +15375,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="R80" t="n">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="R84" t="n">
-        <v>2.47</v>
+        <v>3.48</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="R87" t="n">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.27</v>
+        <v>3.82</v>
       </c>
       <c r="R91" t="n">
-        <v>9.300000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.48</v>
+        <v>1.97</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.25</v>
+        <v>3.88</v>
       </c>
       <c r="R101" t="n">
-        <v>2.7</v>
+        <v>3.99</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.08</v>
+        <v>2.47</v>
       </c>
       <c r="Q38" t="n">
         <v>3.35</v>
       </c>
       <c r="R38" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.28</v>
+        <v>1.97</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="R44" t="n">
-        <v>2.04</v>
+        <v>3.38</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="R50" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.74</v>
+        <v>3.06</v>
       </c>
       <c r="R54" t="n">
-        <v>3.94</v>
+        <v>3.13</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.11</v>
+        <v>3.74</v>
       </c>
       <c r="R55" t="n">
-        <v>3.65</v>
+        <v>3.94</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.57</v>
+        <v>4.32</v>
       </c>
       <c r="R56" t="n">
-        <v>4.9</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.06</v>
+        <v>3.57</v>
       </c>
       <c r="R59" t="n">
-        <v>3.01</v>
+        <v>4.9</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.32</v>
+        <v>3.23</v>
       </c>
       <c r="R61" t="n">
-        <v>8.210000000000001</v>
+        <v>3.58</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R63" t="n">
-        <v>3.72</v>
+        <v>2.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.19</v>
+        <v>3.12</v>
       </c>
       <c r="Q65" t="n">
-        <v>7.7</v>
+        <v>3.45</v>
       </c>
       <c r="R65" t="n">
-        <v>14.1</v>
+        <v>2.15</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.12</v>
+        <v>1.71</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.45</v>
+        <v>3.82</v>
       </c>
       <c r="R72" t="n">
-        <v>2.15</v>
+        <v>4.55</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.27</v>
+        <v>2.47</v>
       </c>
       <c r="Q73" t="n">
-        <v>5.68</v>
+        <v>3.15</v>
       </c>
       <c r="R73" t="n">
-        <v>8.18</v>
+        <v>2.8</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.86</v>
+        <v>1.27</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>5.68</v>
       </c>
       <c r="R76" t="n">
-        <v>1.96</v>
+        <v>8.18</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="R79" t="n">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="R80" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="R84" t="n">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="R85" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.2</v>
+        <v>1.39</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.35</v>
+        <v>5.27</v>
       </c>
       <c r="R87" t="n">
-        <v>2.99</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.27</v>
+        <v>3.82</v>
       </c>
       <c r="R96" t="n">
-        <v>9.300000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.48</v>
+        <v>1.97</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.25</v>
+        <v>3.88</v>
       </c>
       <c r="R99" t="n">
-        <v>2.7</v>
+        <v>3.99</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23649,7 +23649,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
         <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R36" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="Q38" t="n">
         <v>3.35</v>
       </c>
       <c r="R38" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.18</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.99</v>
+        <v>5.2</v>
       </c>
       <c r="R43" t="n">
-        <v>3.58</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.8</v>
+        <v>2.99</v>
       </c>
       <c r="R44" t="n">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.98</v>
+        <v>1.32</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.11</v>
+        <v>4.32</v>
       </c>
       <c r="R50" t="n">
-        <v>3.65</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R54" t="n">
-        <v>3.13</v>
+        <v>2.45</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.74</v>
+        <v>3.23</v>
       </c>
       <c r="R55" t="n">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>8.210000000000001</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.57</v>
+        <v>3.11</v>
       </c>
       <c r="R59" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="R60" t="n">
-        <v>2.45</v>
+        <v>3.13</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.18</v>
+        <v>1.71</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.3</v>
+        <v>3.82</v>
       </c>
       <c r="R69" t="n">
-        <v>2.15</v>
+        <v>4.55</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R70" t="n">
-        <v>3.72</v>
+        <v>2.65</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.71</v>
+        <v>3.18</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>4.55</v>
+        <v>2.15</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.47</v>
+        <v>3.12</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="R73" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14981,17 +14981,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Q75" t="n">
-        <v>7.7</v>
+        <v>5.68</v>
       </c>
       <c r="R75" t="n">
-        <v>14.1</v>
+        <v>8.18</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.68</v>
+        <v>7.7</v>
       </c>
       <c r="R76" t="n">
-        <v>8.18</v>
+        <v>14.1</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="R79" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R82" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R84" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.81</v>
+        <v>3.03</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.82</v>
+        <v>3.19</v>
       </c>
       <c r="R96" t="n">
-        <v>4.33</v>
+        <v>2.31</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="Q36" t="n">
         <v>3.35</v>
       </c>
       <c r="R36" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R37" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.28</v>
+        <v>1.97</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>2.04</v>
+        <v>3.38</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.97</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="R41" t="n">
-        <v>3.38</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>8.550000000000001</v>
+        <v>3.28</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.2</v>
+        <v>3.68</v>
       </c>
       <c r="R43" t="n">
-        <v>1.28</v>
+        <v>2.04</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.32</v>
+        <v>3.23</v>
       </c>
       <c r="R50" t="n">
-        <v>8.210000000000001</v>
+        <v>3.58</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.57</v>
+        <v>3.06</v>
       </c>
       <c r="R51" t="n">
-        <v>4.9</v>
+        <v>3.13</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,17 +11041,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.23</v>
+        <v>3.74</v>
       </c>
       <c r="R55" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.06</v>
+        <v>3.57</v>
       </c>
       <c r="R60" t="n">
-        <v>3.13</v>
+        <v>4.9</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.9</v>
+        <v>2.47</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R66" t="n">
-        <v>3.72</v>
+        <v>2.8</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>8.18</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.71</v>
+        <v>3.86</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="R69" t="n">
-        <v>4.55</v>
+        <v>1.96</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="R70" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14981,17 +14981,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.68</v>
+        <v>7.7</v>
       </c>
       <c r="R75" t="n">
-        <v>8.18</v>
+        <v>14.1</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.47</v>
+        <v>2.6</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.6</v>
+        <v>3.47</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R78" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.33</v>
+        <v>2.22</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.94</v>
+        <v>3.2</v>
       </c>
       <c r="R79" t="n">
-        <v>2.17</v>
+        <v>3.05</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="R81" t="n">
-        <v>3.48</v>
+        <v>2.47</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.55</v>
+        <v>3.94</v>
       </c>
       <c r="R82" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="R84" t="n">
-        <v>2.47</v>
+        <v>3.48</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="R88" t="n">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.03</v>
+        <v>1.81</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.19</v>
+        <v>3.82</v>
       </c>
       <c r="R96" t="n">
-        <v>2.31</v>
+        <v>4.33</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="Q37" t="n">
         <v>3.35</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>8.550000000000001</v>
+        <v>3.28</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.2</v>
+        <v>3.68</v>
       </c>
       <c r="R41" t="n">
-        <v>1.28</v>
+        <v>2.04</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.06</v>
+        <v>3.74</v>
       </c>
       <c r="R51" t="n">
-        <v>3.13</v>
+        <v>3.94</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.74</v>
+        <v>3.23</v>
       </c>
       <c r="R55" t="n">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R56" t="n">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="R58" t="n">
-        <v>2.45</v>
+        <v>3.13</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="R59" t="n">
-        <v>3.65</v>
+        <v>3.01</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.9</v>
+        <v>3.18</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>3.72</v>
+        <v>2.15</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.71</v>
+        <v>3.12</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="R67" t="n">
-        <v>4.55</v>
+        <v>2.15</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.27</v>
+        <v>3.86</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.68</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>8.18</v>
+        <v>1.96</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>8.18</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14981,17 +14981,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.19</v>
+        <v>2.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>7.7</v>
+        <v>3.25</v>
       </c>
       <c r="R75" t="n">
-        <v>14.1</v>
+        <v>2.65</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.6</v>
+        <v>3.47</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R77" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.47</v>
+        <v>2.6</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.33</v>
+        <v>2.13</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.94</v>
+        <v>3.53</v>
       </c>
       <c r="R82" t="n">
-        <v>2.17</v>
+        <v>3.48</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="R96" t="n">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.97</v>
+        <v>2.48</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="R101" t="n">
-        <v>3.99</v>
+        <v>2.7</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="Q37" t="n">
         <v>3.35</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.97</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="R40" t="n">
-        <v>3.38</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.28</v>
+        <v>1.97</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>2.04</v>
+        <v>3.38</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.18</v>
+        <v>3.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.99</v>
+        <v>3.68</v>
       </c>
       <c r="R42" t="n">
-        <v>3.58</v>
+        <v>2.04</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>8.550000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.2</v>
+        <v>2.99</v>
       </c>
       <c r="R44" t="n">
-        <v>1.28</v>
+        <v>3.58</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,17 +10450,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="R52" t="n">
-        <v>3.65</v>
+        <v>3.01</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,17 +11041,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.06</v>
+        <v>4.32</v>
       </c>
       <c r="R58" t="n">
-        <v>3.13</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.06</v>
+        <v>3.57</v>
       </c>
       <c r="R59" t="n">
-        <v>3.01</v>
+        <v>4.9</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.57</v>
+        <v>3.06</v>
       </c>
       <c r="R60" t="n">
-        <v>4.9</v>
+        <v>3.13</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.32</v>
+        <v>3.74</v>
       </c>
       <c r="R61" t="n">
-        <v>8.210000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,10 +12818,10 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R63" t="n">
         <v>2.15</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.12</v>
+        <v>3.86</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.86</v>
+        <v>1.71</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>3.82</v>
       </c>
       <c r="R68" t="n">
-        <v>1.96</v>
+        <v>4.55</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>8.18</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.25</v>
+        <v>5.68</v>
       </c>
       <c r="R75" t="n">
-        <v>2.65</v>
+        <v>8.18</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.33</v>
+        <v>2.13</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.94</v>
+        <v>3.53</v>
       </c>
       <c r="R80" t="n">
-        <v>2.17</v>
+        <v>3.48</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R81" t="n">
-        <v>2.47</v>
+        <v>3.05</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="R82" t="n">
-        <v>3.48</v>
+        <v>2.47</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.55</v>
+        <v>3.94</v>
       </c>
       <c r="R85" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.97</v>
+        <v>2.48</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="R100" t="n">
-        <v>3.99</v>
+        <v>2.7</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.48</v>
+        <v>1.97</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.25</v>
+        <v>3.88</v>
       </c>
       <c r="R101" t="n">
-        <v>2.7</v>
+        <v>3.99</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G119" t="n">

--- a/jogos_2026-04-10.xlsx
+++ b/jogos_2026-04-10.xlsx
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,76 +1195,76 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="S4" t="n">
-        <v>4.02</v>
+        <v>4.07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>3.01</v>
+        <v>3.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="X4" t="n">
         <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.42</v>
+        <v>4.65</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.01</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AN4" t="n">
         <v>1.31</v>
@@ -1309,16 +1309,16 @@
         <v>1.65</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BF4" t="n">
         <v>1.07</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1992,70 +1992,70 @@
         <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.05</v>
+        <v>3.61</v>
       </c>
       <c r="R12" t="n">
-        <v>7.34</v>
+        <v>4.99</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.97</v>
+        <v>3.28</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="R41" t="n">
-        <v>3.38</v>
+        <v>2.04</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.28</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.68</v>
+        <v>5.2</v>
       </c>
       <c r="R42" t="n">
-        <v>2.04</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.99</v>
+        <v>3.8</v>
       </c>
       <c r="R44" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,17 +10450,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.06</v>
+        <v>3.57</v>
       </c>
       <c r="R52" t="n">
-        <v>3.01</v>
+        <v>4.9</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="R54" t="n">
-        <v>2.45</v>
+        <v>3.13</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.32</v>
+        <v>2.85</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.32</v>
+        <v>2.94</v>
       </c>
       <c r="R58" t="n">
-        <v>8.210000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.57</v>
+        <v>3.23</v>
       </c>
       <c r="R59" t="n">
-        <v>4.9</v>
+        <v>3.58</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.74</v>
+        <v>3.11</v>
       </c>
       <c r="R61" t="n">
-        <v>3.94</v>
+        <v>3.65</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.12</v>
+        <v>2.47</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="R63" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.47</v>
+        <v>3.12</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="R64" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R66" t="n">
-        <v>3.72</v>
+        <v>2.65</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="R68" t="n">
-        <v>4.55</v>
+        <v>3.72</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.25</v>
+        <v>3.82</v>
       </c>
       <c r="R69" t="n">
-        <v>2.65</v>
+        <v>4.55</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14193,17 +14193,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>8.18</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.68</v>
+        <v>7.7</v>
       </c>
       <c r="R75" t="n">
-        <v>8.18</v>
+        <v>14.1</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.22</v>
+        <v>3.33</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.2</v>
+        <v>3.94</v>
       </c>
       <c r="R81" t="n">
-        <v>3.05</v>
+        <v>2.17</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.94</v>
+        <v>3.55</v>
       </c>
       <c r="R85" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.27</v>
+        <v>3.35</v>
       </c>
       <c r="R90" t="n">
-        <v>9.300000000000001</v>
+        <v>2.99</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="R92" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.35</v>
+        <v>3.82</v>
       </c>
       <c r="R93" t="n">
-        <v>2.99</v>
+        <v>4.33</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
